--- a/target/test-classes/UI_dataSheet.xlsx
+++ b/target/test-classes/UI_dataSheet.xlsx
@@ -22,13 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
   <si>
-    <t>TestName8945jkf02</t>
+    <t>TestName8945jkf09</t>
   </si>
   <si>
-    <t>testemail390nvj@email.com02</t>
+    <t>testemail390nvj@email.com09</t>
   </si>
   <si>
-    <t>Pasword98923489</t>
+    <t>Pasword98923496</t>
   </si>
 </sst>
 </file>
@@ -376,12 +376,12 @@
         <v>2</v>
       </c>
       <c r="D1">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1"/>
+    <hyperlink ref="B1" r:id="rId1" display="testemail390nvj@email.com02"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -406,7 +406,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1"/>
+    <hyperlink ref="A1" r:id="rId1" display="testemail390nvj@email.com02"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/target/test-classes/UI_dataSheet.xlsx
+++ b/target/test-classes/UI_dataSheet.xlsx
@@ -22,13 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
   <si>
-    <t>TestName8945jkf09</t>
+    <t>TestName8945jkf20</t>
   </si>
   <si>
-    <t>testemail390nvj@email.com09</t>
+    <t>testemail390nvj@email.com20</t>
   </si>
   <si>
-    <t>Pasword98923496</t>
+    <t>Pasword98923507</t>
   </si>
 </sst>
 </file>
@@ -376,7 +376,7 @@
         <v>2</v>
       </c>
       <c r="D1">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
